--- a/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu475000_stage1b_rep2.xlsx
+++ b/experiment_results/wedos_grid/rtt_bursts_S2_atk1pct_wu475000_stage1b_rep2.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>200638</t>
+          <t>119499</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>234913</t>
+          <t>116512</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>227314</t>
+          <t>111900</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>240469</t>
+          <t>129667</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>252053</t>
+          <t>123483</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>239453</t>
+          <t>117067</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>224854</t>
+          <t>108884</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>219885</t>
+          <t>112099</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>226251</t>
+          <t>115250</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>223904</t>
+          <t>109752</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>208083</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>196715</t>
+          <t>98384</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>195671</t>
+          <t>98384</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
